--- a/Result/profitability/6141.xlsx
+++ b/Result/profitability/6141.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.07875</v>
+        <v>-0.95875</v>
       </c>
       <c r="N2" t="n">
-        <v>7.77375</v>
+        <v>10.14</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7775</v>
+        <v>-0.60125</v>
       </c>
       <c r="N3" t="n">
-        <v>11.41125</v>
+        <v>11.50375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.9</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4075</v>
+        <v>-0.485</v>
       </c>
       <c r="N4" t="n">
-        <v>11.77125</v>
+        <v>10.41625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.42125</v>
+        <v>-0.32125</v>
       </c>
       <c r="N5" t="n">
-        <v>10.5875</v>
+        <v>11.26375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.22375</v>
+        <v>-0.24125</v>
       </c>
       <c r="N6" t="n">
-        <v>11.835</v>
+        <v>12.75875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>-0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.16125</v>
+        <v>0.09000000000000007</v>
       </c>
       <c r="N7" t="n">
-        <v>12.4475</v>
+        <v>13.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2162500000000001</v>
+        <v>0.2075000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>14.09375</v>
+        <v>14.89</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.54</v>
       </c>
       <c r="M11" t="n">
-        <v>0.315</v>
+        <v>0.3150000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>14.055</v>
@@ -2026,7 +2026,7 @@
         <v>0.53</v>
       </c>
       <c r="M13" t="n">
-        <v>0.31875</v>
+        <v>0.3187500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>14.395</v>
@@ -9335,24 +9335,24 @@
         <v>465</v>
       </c>
       <c r="D71" t="n">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="F71" t="n">
-        <v>0.49</v>
+        <v>7.39</v>
       </c>
       <c r="G71" t="n">
-        <v>-111</v>
+        <v>-79</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-23.89%</t>
+          <t>-16.99%</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-64</v>
+        <v>-96</v>
       </c>
       <c r="J71" t="n">
         <v>-175</v>
@@ -9367,7 +9367,7 @@
         <v>-1.48125</v>
       </c>
       <c r="N71" t="n">
-        <v>-3.017500000000001</v>
+        <v>-2.155</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9400,10 +9400,10 @@
         <v>47.33333333333334</v>
       </c>
       <c r="Y71" t="n">
-        <v>-23.15</v>
+        <v>-16.25</v>
       </c>
       <c r="Z71" t="n">
-        <v>-0.9792724196277496</v>
+        <v>-0.6873942470389172</v>
       </c>
       <c r="AA71" t="n">
         <v>0.48</v>
@@ -9412,10 +9412,10 @@
         <v>-0.2487046632124352</v>
       </c>
       <c r="AC71" t="n">
-        <v>14.85</v>
+        <v>21.75</v>
       </c>
       <c r="AD71" t="n">
-        <v>-1.034122562674095</v>
+        <v>-1.514623955431755</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -9462,24 +9462,24 @@
         <v>432</v>
       </c>
       <c r="D72" t="n">
-        <v>406</v>
+        <v>438</v>
       </c>
       <c r="E72" t="n">
-        <v>26</v>
+        <v>-6</v>
       </c>
       <c r="F72" t="n">
-        <v>5.94</v>
+        <v>-1.49</v>
       </c>
       <c r="G72" t="n">
-        <v>-61</v>
+        <v>-93</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-14.15%</t>
+          <t>-21.58%</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>-17</v>
+        <v>15</v>
       </c>
       <c r="J72" t="n">
         <v>-78</v>
@@ -9494,7 +9494,7 @@
         <v>-1.465</v>
       </c>
       <c r="N72" t="n">
-        <v>-2.3125</v>
+        <v>-2.378750000000001</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -9527,10 +9527,10 @@
         <v>-0.6482758620689655</v>
       </c>
       <c r="Y72" t="n">
-        <v>5.45</v>
+        <v>-8.879999999999999</v>
       </c>
       <c r="Z72" t="n">
-        <v>11.12244897959184</v>
+        <v>-1.201623815967524</v>
       </c>
       <c r="AA72" t="n">
         <v>1.1</v>
@@ -9539,10 +9539,10 @@
         <v>-0.6832298136645962</v>
       </c>
       <c r="AC72" t="n">
-        <v>12.07</v>
+        <v>4.64</v>
       </c>
       <c r="AD72" t="n">
-        <v>-1.969004893964111</v>
+        <v>-0.7569331158238173</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -9551,7 +9551,7 @@
         <v>1</v>
       </c>
       <c r="AG72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="n">
         <v>1</v>
@@ -9621,7 +9621,7 @@
         <v>-1.5875</v>
       </c>
       <c r="N73" t="n">
-        <v>0.1549999999999996</v>
+        <v>0.08874999999999955</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9654,10 +9654,10 @@
         <v>4.215686274509804</v>
       </c>
       <c r="Y73" t="n">
-        <v>-2.63</v>
+        <v>4.8</v>
       </c>
       <c r="Z73" t="n">
-        <v>-0.4427609427609428</v>
+        <v>-3.221476510067114</v>
       </c>
       <c r="AA73" t="n">
         <v>-0.6000000000000001</v>
@@ -9678,7 +9678,7 @@
         <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH73" t="n">
         <v>0</v>
@@ -9748,7 +9748,7 @@
         <v>-1.35375</v>
       </c>
       <c r="N74" t="n">
-        <v>3.98875</v>
+        <v>3.9225</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6141</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>599</v>
+      </c>
+      <c r="D75" t="n">
+        <v>519</v>
+      </c>
+      <c r="E75" t="n">
+        <v>80</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-32</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.39%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-58</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-90</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-74</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-1.19375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7.383749999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.07000000000000006</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1206896551724139</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.9152298850574714</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5517241379310345</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.8037889039242221</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
